--- a/Team-Data/2008-09/2-20-2008-09.xlsx
+++ b/Team-Data/2008-09/2-20-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E2" t="n">
         <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>0.582</v>
+        <v>0.593</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -691,28 +758,28 @@
         <v>20.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O2" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P2" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Q2" t="n">
         <v>0.735</v>
       </c>
       <c r="R2" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S2" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T2" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U2" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V2" t="n">
         <v>12.9</v>
@@ -727,19 +794,19 @@
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB2" t="n">
         <v>98.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
         <v>9</v>
@@ -751,28 +818,28 @@
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
         <v>22</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL2" t="n">
         <v>8</v>
       </c>
       <c r="AM2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AP2" t="n">
         <v>8</v>
@@ -781,34 +848,34 @@
         <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
         <v>19</v>
       </c>
       <c r="AT2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV2" t="n">
         <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
         <v>19</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -843,22 +910,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3" t="n">
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0.782</v>
+        <v>0.786</v>
       </c>
       <c r="H3" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J3" t="n">
         <v>77.3</v>
@@ -867,64 +934,64 @@
         <v>0.483</v>
       </c>
       <c r="L3" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M3" t="n">
         <v>16.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.386</v>
+        <v>0.383</v>
       </c>
       <c r="O3" t="n">
         <v>20.1</v>
       </c>
       <c r="P3" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.777</v>
+        <v>0.773</v>
       </c>
       <c r="R3" t="n">
         <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
         <v>15.8</v>
       </c>
       <c r="W3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y3" t="n">
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.2</v>
+        <v>101</v>
       </c>
       <c r="AC3" t="n">
         <v>9.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>3</v>
@@ -933,34 +1000,34 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="n">
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
         <v>17</v>
@@ -981,10 +1048,10 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -1025,34 +1092,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" t="n">
         <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4</v>
+        <v>0.407</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J4" t="n">
-        <v>76.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L4" t="n">
         <v>5.8</v>
       </c>
       <c r="M4" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="N4" t="n">
         <v>0.364</v>
@@ -1061,22 +1128,22 @@
         <v>17.9</v>
       </c>
       <c r="P4" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="R4" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S4" t="n">
         <v>28.7</v>
       </c>
       <c r="T4" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="U4" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V4" t="n">
         <v>15.5</v>
@@ -1088,7 +1155,7 @@
         <v>4.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z4" t="n">
         <v>22.3</v>
@@ -1097,22 +1164,22 @@
         <v>21.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.8</v>
+        <v>-1.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF4" t="n">
         <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
         <v>2</v>
@@ -1121,16 +1188,16 @@
         <v>30</v>
       </c>
       <c r="AJ4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
       </c>
       <c r="AM4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN4" t="n">
         <v>18</v>
@@ -1148,19 +1215,19 @@
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT4" t="n">
         <v>25</v>
       </c>
       <c r="AU4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV4" t="n">
         <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1178,7 +1245,7 @@
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -1222,10 +1289,10 @@
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K5" t="n">
         <v>0.451</v>
@@ -1234,31 +1301,31 @@
         <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.377</v>
+        <v>0.376</v>
       </c>
       <c r="O5" t="n">
         <v>19.3</v>
       </c>
       <c r="P5" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.792</v>
+        <v>0.788</v>
       </c>
       <c r="R5" t="n">
         <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U5" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V5" t="n">
         <v>15.1</v>
@@ -1270,22 +1337,22 @@
         <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" t="n">
         <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.6</v>
+        <v>100.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1312,7 +1379,7 @@
         <v>22</v>
       </c>
       <c r="AM5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN5" t="n">
         <v>9</v>
@@ -1321,13 +1388,13 @@
         <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS5" t="n">
         <v>14</v>
@@ -1342,7 +1409,7 @@
         <v>24</v>
       </c>
       <c r="AW5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
         <v>5</v>
@@ -1354,13 +1421,13 @@
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB5" t="n">
         <v>12</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -1392,88 +1459,88 @@
         <v>52</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.788</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J6" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.385</v>
+        <v>0.38</v>
       </c>
       <c r="O6" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P6" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q6" t="n">
         <v>0.752</v>
       </c>
       <c r="R6" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S6" t="n">
-        <v>31</v>
+        <v>31.2</v>
       </c>
       <c r="T6" t="n">
-        <v>41.7</v>
+        <v>41.9</v>
       </c>
       <c r="U6" t="n">
         <v>20.1</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W6" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X6" t="n">
         <v>5.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.2</v>
+        <v>100.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE6" t="n">
         <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
         <v>2</v>
@@ -1491,25 +1558,25 @@
         <v>5</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO6" t="n">
         <v>22</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>23</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1524,7 +1591,7 @@
         <v>6</v>
       </c>
       <c r="AW6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
         <v>4</v>
@@ -1533,13 +1600,13 @@
         <v>4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA6" t="n">
         <v>23</v>
       </c>
       <c r="BB6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -1571,28 +1638,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7" t="n">
         <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>0.593</v>
+        <v>0.604</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J7" t="n">
         <v>83</v>
       </c>
       <c r="K7" t="n">
-        <v>0.459</v>
+        <v>0.461</v>
       </c>
       <c r="L7" t="n">
         <v>6.8</v>
@@ -1601,34 +1668,34 @@
         <v>19.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="O7" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="P7" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="R7" t="n">
         <v>11.1</v>
       </c>
       <c r="S7" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T7" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U7" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V7" t="n">
         <v>13.2</v>
       </c>
       <c r="W7" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X7" t="n">
         <v>5.5</v>
@@ -1643,25 +1710,25 @@
         <v>19.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.8</v>
+        <v>101.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG7" t="n">
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI7" t="n">
         <v>6</v>
@@ -1691,25 +1758,25 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="n">
         <v>9</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
         <v>14</v>
       </c>
       <c r="AX7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
@@ -1721,7 +1788,7 @@
         <v>26</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" t="n">
         <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>0.673</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
@@ -1771,7 +1838,7 @@
         <v>37</v>
       </c>
       <c r="J8" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0.472</v>
@@ -1780,28 +1847,28 @@
         <v>6.5</v>
       </c>
       <c r="M8" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.368</v>
+        <v>0.366</v>
       </c>
       <c r="O8" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="P8" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R8" t="n">
         <v>10.3</v>
       </c>
       <c r="S8" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T8" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U8" t="n">
         <v>22.5</v>
@@ -1819,28 +1886,28 @@
         <v>5.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.4</v>
+        <v>103.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
@@ -1855,7 +1922,7 @@
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM8" t="n">
         <v>18</v>
@@ -1882,7 +1949,7 @@
         <v>18</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
         <v>26</v>
@@ -1900,13 +1967,13 @@
         <v>25</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
         <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
         <v>15</v>
@@ -2034,7 +2101,7 @@
         <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL9" t="n">
         <v>27</v>
@@ -2049,7 +2116,7 @@
         <v>29</v>
       </c>
       <c r="AP9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
@@ -2073,7 +2140,7 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY9" t="n">
         <v>5</v>
@@ -2085,7 +2152,7 @@
         <v>24</v>
       </c>
       <c r="BB9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC9" t="n">
         <v>17</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -2195,19 +2262,19 @@
         <v>-3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
       </c>
       <c r="AF10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2216,7 +2283,7 @@
         <v>2</v>
       </c>
       <c r="AK10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL10" t="n">
         <v>14</v>
@@ -2237,7 +2304,7 @@
         <v>10</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS10" t="n">
         <v>15</v>
@@ -2258,13 +2325,13 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ10" t="n">
         <v>22</v>
       </c>
       <c r="BA10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB10" t="n">
         <v>2</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" t="n">
         <v>21</v>
       </c>
       <c r="G11" t="n">
-        <v>0.618</v>
+        <v>0.611</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="J11" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="K11" t="n">
         <v>0.445</v>
@@ -2326,34 +2393,34 @@
         <v>7.7</v>
       </c>
       <c r="M11" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.377</v>
+        <v>0.375</v>
       </c>
       <c r="O11" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="P11" t="n">
         <v>24.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R11" t="n">
         <v>10.9</v>
       </c>
       <c r="S11" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T11" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U11" t="n">
         <v>20.5</v>
       </c>
       <c r="V11" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="W11" t="n">
         <v>6.8</v>
@@ -2362,7 +2429,7 @@
         <v>3.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z11" t="n">
         <v>18.9</v>
@@ -2371,25 +2438,25 @@
         <v>20.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC11" t="n">
         <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
         <v>27</v>
@@ -2398,7 +2465,7 @@
         <v>16</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL11" t="n">
         <v>6</v>
@@ -2407,13 +2474,13 @@
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ11" t="n">
         <v>4</v>
@@ -2425,19 +2492,19 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV11" t="n">
         <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY11" t="n">
         <v>25</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -2481,22 +2548,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F12" t="n">
         <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>0.404</v>
+        <v>0.393</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="J12" t="n">
         <v>86</v>
@@ -2508,10 +2575,10 @@
         <v>7.8</v>
       </c>
       <c r="M12" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.37</v>
+        <v>0.368</v>
       </c>
       <c r="O12" t="n">
         <v>19.1</v>
@@ -2520,7 +2587,7 @@
         <v>23.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.806</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R12" t="n">
         <v>11.1</v>
@@ -2538,10 +2605,10 @@
         <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y12" t="n">
         <v>5.5</v>
@@ -2550,16 +2617,16 @@
         <v>23.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.7</v>
+        <v>104.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.1</v>
+        <v>-2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
@@ -2568,7 +2635,7 @@
         <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH12" t="n">
         <v>8</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
         <v>16</v>
@@ -2610,13 +2677,13 @@
         <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -2634,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -2741,22 +2808,22 @@
         <v>-8.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
       </c>
       <c r="AF13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH13" t="n">
         <v>4</v>
       </c>
       <c r="AI13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2768,7 +2835,7 @@
         <v>19</v>
       </c>
       <c r="AM13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN13" t="n">
         <v>24</v>
@@ -2789,22 +2856,22 @@
         <v>25</v>
       </c>
       <c r="AT13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV13" t="n">
         <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ13" t="n">
         <v>16</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -2857,34 +2924,34 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="K14" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="L14" t="n">
         <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.366</v>
+        <v>0.37</v>
       </c>
       <c r="O14" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="P14" t="n">
-        <v>27.1</v>
+        <v>26.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R14" t="n">
         <v>12.8</v>
@@ -2893,37 +2960,37 @@
         <v>31.9</v>
       </c>
       <c r="T14" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="V14" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W14" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y14" t="n">
         <v>4.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>109.1</v>
+        <v>108.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2935,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2944,7 +3011,7 @@
         <v>4</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2962,13 +3029,13 @@
         <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2986,10 +3053,10 @@
         <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -3027,28 +3094,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
         <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G15" t="n">
-        <v>0.273</v>
+        <v>0.278</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J15" t="n">
-        <v>77.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L15" t="n">
         <v>4.6</v>
@@ -3057,55 +3124,55 @@
         <v>13.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.334</v>
+        <v>0.335</v>
       </c>
       <c r="O15" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="P15" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.754</v>
+        <v>0.752</v>
       </c>
       <c r="R15" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="S15" t="n">
         <v>28.7</v>
       </c>
       <c r="T15" t="n">
-        <v>39.4</v>
+        <v>39.1</v>
       </c>
       <c r="U15" t="n">
         <v>16.7</v>
       </c>
       <c r="V15" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X15" t="n">
         <v>4.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA15" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.5</v>
+        <v>93.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.3</v>
+        <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3123,7 +3190,7 @@
         <v>29</v>
       </c>
       <c r="AJ15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK15" t="n">
         <v>23</v>
@@ -3141,19 +3208,19 @@
         <v>12</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
@@ -3168,7 +3235,7 @@
         <v>22</v>
       </c>
       <c r="AY15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ15" t="n">
         <v>21</v>
@@ -3177,7 +3244,7 @@
         <v>9</v>
       </c>
       <c r="BB15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3299,7 +3366,7 @@
         <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
         <v>18</v>
@@ -3335,13 +3402,13 @@
         <v>24</v>
       </c>
       <c r="AT16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
         <v>5</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -3418,28 +3485,28 @@
         <v>5.8</v>
       </c>
       <c r="M17" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
       <c r="O17" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="P17" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.782</v>
+        <v>0.783</v>
       </c>
       <c r="R17" t="n">
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T17" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="U17" t="n">
         <v>21.5</v>
@@ -3454,19 +3521,19 @@
         <v>3.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3481,16 +3548,16 @@
         <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ17" t="n">
         <v>11</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="n">
         <v>23</v>
@@ -3523,16 +3590,16 @@
         <v>10</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E18" t="n">
         <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3591,28 +3658,28 @@
         <v>36.9</v>
       </c>
       <c r="J18" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
       <c r="K18" t="n">
         <v>0.44</v>
       </c>
       <c r="L18" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M18" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.344</v>
+        <v>0.342</v>
       </c>
       <c r="O18" t="n">
         <v>19.2</v>
       </c>
       <c r="P18" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.766</v>
+        <v>0.772</v>
       </c>
       <c r="R18" t="n">
         <v>12.5</v>
@@ -3627,10 +3694,10 @@
         <v>20.4</v>
       </c>
       <c r="V18" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W18" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="X18" t="n">
         <v>4.1</v>
@@ -3642,16 +3709,16 @@
         <v>21.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.7</v>
+        <v>-3.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3684,13 +3751,13 @@
         <v>26</v>
       </c>
       <c r="AO18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP18" t="n">
         <v>14</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AR18" t="n">
         <v>4</v>
@@ -3702,13 +3769,13 @@
         <v>10</v>
       </c>
       <c r="AU18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX18" t="n">
         <v>25</v>
@@ -3720,10 +3787,10 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -3755,58 +3822,58 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E19" t="n">
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G19" t="n">
-        <v>0.429</v>
+        <v>0.436</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
       </c>
       <c r="I19" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="J19" t="n">
-        <v>80.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L19" t="n">
         <v>7.7</v>
       </c>
       <c r="M19" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0.376</v>
+        <v>0.38</v>
       </c>
       <c r="O19" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P19" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.775</v>
+        <v>0.777</v>
       </c>
       <c r="R19" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S19" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T19" t="n">
         <v>40.5</v>
       </c>
       <c r="U19" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="V19" t="n">
         <v>13.4</v>
@@ -3815,31 +3882,31 @@
         <v>6.9</v>
       </c>
       <c r="X19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y19" t="n">
         <v>5</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AA19" t="n">
         <v>20.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.7</v>
+        <v>-2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
         <v>19</v>
@@ -3863,19 +3930,19 @@
         <v>7</v>
       </c>
       <c r="AN19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
         <v>20</v>
@@ -3890,10 +3957,10 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY19" t="n">
         <v>17</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -3937,64 +4004,64 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E20" t="n">
         <v>32</v>
       </c>
       <c r="F20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>0.604</v>
+        <v>0.615</v>
       </c>
       <c r="H20" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="J20" t="n">
-        <v>76.8</v>
+        <v>76.5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L20" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="N20" t="n">
         <v>0.384</v>
       </c>
       <c r="O20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P20" t="n">
         <v>23</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="R20" t="n">
         <v>9.4</v>
       </c>
       <c r="S20" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="T20" t="n">
-        <v>38.7</v>
+        <v>38.5</v>
       </c>
       <c r="U20" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V20" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="W20" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X20" t="n">
         <v>4.3</v>
@@ -4003,37 +4070,37 @@
         <v>3.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="AA20" t="n">
         <v>21</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.09999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AE20" t="n">
         <v>9</v>
       </c>
       <c r="AF20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG20" t="n">
         <v>8</v>
       </c>
-      <c r="AG20" t="n">
-        <v>9</v>
-      </c>
       <c r="AH20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AI20" t="n">
         <v>28</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK20" t="n">
         <v>13</v>
@@ -4045,7 +4112,7 @@
         <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AO20" t="n">
         <v>21</v>
@@ -4060,10 +4127,10 @@
         <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AU20" t="n">
         <v>27</v>
@@ -4084,7 +4151,7 @@
         <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -4119,85 +4186,85 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F21" t="n">
         <v>31</v>
       </c>
       <c r="G21" t="n">
-        <v>0.426</v>
+        <v>0.415</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J21" t="n">
-        <v>86.8</v>
+        <v>86.7</v>
       </c>
       <c r="K21" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L21" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="M21" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.36</v>
+        <v>0.358</v>
       </c>
       <c r="O21" t="n">
         <v>17.9</v>
       </c>
       <c r="P21" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.799</v>
+        <v>0.796</v>
       </c>
       <c r="R21" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S21" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="T21" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U21" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V21" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W21" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z21" t="n">
         <v>20.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>105.6</v>
+        <v>105.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.9</v>
+        <v>-2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
@@ -4209,7 +4276,7 @@
         <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4218,10 +4285,10 @@
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM21" t="n">
         <v>1</v>
@@ -4233,7 +4300,7 @@
         <v>23</v>
       </c>
       <c r="AP21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ21" t="n">
         <v>7</v>
@@ -4242,10 +4309,10 @@
         <v>15</v>
       </c>
       <c r="AS21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AU21" t="n">
         <v>8</v>
@@ -4254,7 +4321,7 @@
         <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>24</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4272,7 +4339,7 @@
         <v>4</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -4301,61 +4368,61 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E22" t="n">
         <v>13</v>
       </c>
       <c r="F22" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>0.236</v>
+        <v>0.241</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J22" t="n">
-        <v>81.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>0.449</v>
       </c>
       <c r="L22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M22" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.373</v>
+        <v>0.366</v>
       </c>
       <c r="O22" t="n">
         <v>20.1</v>
       </c>
       <c r="P22" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R22" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S22" t="n">
         <v>30.9</v>
       </c>
       <c r="T22" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U22" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V22" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W22" t="n">
         <v>6.8</v>
@@ -4367,19 +4434,19 @@
         <v>5.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB22" t="n">
-        <v>97.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>-6.1</v>
+        <v>-5.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4391,7 +4458,7 @@
         <v>27</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>14</v>
@@ -4400,16 +4467,16 @@
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM22" t="n">
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AO22" t="n">
         <v>8</v>
@@ -4418,7 +4485,7 @@
         <v>9</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
         <v>5</v>
@@ -4430,28 +4497,28 @@
         <v>5</v>
       </c>
       <c r="AU22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ22" t="n">
         <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC22" t="n">
         <v>26</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -4483,25 +4550,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E23" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F23" t="n">
         <v>14</v>
       </c>
       <c r="G23" t="n">
-        <v>0.741</v>
+        <v>0.736</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J23" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="K23" t="n">
         <v>0.458</v>
@@ -4510,10 +4577,10 @@
         <v>10.4</v>
       </c>
       <c r="M23" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.394</v>
+        <v>0.396</v>
       </c>
       <c r="O23" t="n">
         <v>19.8</v>
@@ -4522,7 +4589,7 @@
         <v>27.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="R23" t="n">
         <v>10.1</v>
@@ -4531,7 +4598,7 @@
         <v>33.1</v>
       </c>
       <c r="T23" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U23" t="n">
         <v>19.3</v>
@@ -4540,13 +4607,13 @@
         <v>14.1</v>
       </c>
       <c r="W23" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X23" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z23" t="n">
         <v>20.3</v>
@@ -4555,13 +4622,13 @@
         <v>22.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>101.8</v>
+        <v>102</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4576,7 +4643,7 @@
         <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AJ23" t="n">
         <v>26</v>
@@ -4585,7 +4652,7 @@
         <v>10</v>
       </c>
       <c r="AL23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM23" t="n">
         <v>2</v>
@@ -4594,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="AO23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4609,7 +4676,7 @@
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU23" t="n">
         <v>29</v>
@@ -4618,7 +4685,7 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX23" t="n">
         <v>9</v>
@@ -4627,7 +4694,7 @@
         <v>3</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4758,7 +4825,7 @@
         <v>27</v>
       </c>
       <c r="AI24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ24" t="n">
         <v>14</v>
@@ -4767,7 +4834,7 @@
         <v>16</v>
       </c>
       <c r="AL24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM24" t="n">
         <v>29</v>
@@ -4779,7 +4846,7 @@
         <v>18</v>
       </c>
       <c r="AP24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ24" t="n">
         <v>26</v>
@@ -4791,7 +4858,7 @@
         <v>17</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU24" t="n">
         <v>17</v>
@@ -4803,16 +4870,16 @@
         <v>6</v>
       </c>
       <c r="AX24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY24" t="n">
         <v>16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB24" t="n">
         <v>24</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -4847,37 +4914,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F25" t="n">
         <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>0.574</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>39.5</v>
+        <v>39.3</v>
       </c>
       <c r="J25" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="K25" t="n">
-        <v>0.501</v>
+        <v>0.499</v>
       </c>
       <c r="L25" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M25" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.385</v>
+        <v>0.381</v>
       </c>
       <c r="O25" t="n">
         <v>20.9</v>
@@ -4886,7 +4953,7 @@
         <v>27.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R25" t="n">
         <v>10.1</v>
@@ -4898,13 +4965,13 @@
         <v>42</v>
       </c>
       <c r="U25" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="V25" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W25" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="X25" t="n">
         <v>4.8</v>
@@ -4916,22 +4983,22 @@
         <v>20.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>106.4</v>
+        <v>105.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG25" t="n">
         <v>13</v>
@@ -4943,49 +5010,49 @@
         <v>2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>4</v>
       </c>
       <c r="AP25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ25" t="n">
         <v>20</v>
       </c>
       <c r="AR25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT25" t="n">
         <v>13</v>
       </c>
       <c r="AU25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV25" t="n">
         <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX25" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AY25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -5032,25 +5099,25 @@
         <v>53</v>
       </c>
       <c r="E26" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>0.642</v>
+        <v>0.623</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.7</v>
+        <v>36.4</v>
       </c>
       <c r="J26" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.465</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
@@ -5059,31 +5126,31 @@
         <v>19.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="O26" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P26" t="n">
         <v>24.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.764</v>
+        <v>0.762</v>
       </c>
       <c r="R26" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="T26" t="n">
         <v>41.1</v>
       </c>
       <c r="U26" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V26" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W26" t="n">
         <v>6.9</v>
@@ -5098,16 +5165,16 @@
         <v>21.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5122,13 +5189,13 @@
         <v>12</v>
       </c>
       <c r="AI26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
@@ -5137,16 +5204,16 @@
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AO26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP26" t="n">
         <v>17</v>
       </c>
       <c r="AQ26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5158,13 +5225,13 @@
         <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX26" t="n">
         <v>12</v>
@@ -5176,13 +5243,13 @@
         <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F27" t="n">
         <v>44</v>
       </c>
       <c r="G27" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
@@ -5229,28 +5296,28 @@
         <v>36.1</v>
       </c>
       <c r="J27" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L27" t="n">
         <v>6.5</v>
       </c>
       <c r="M27" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O27" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="P27" t="n">
-        <v>25.8</v>
+        <v>25.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.805</v>
+        <v>0.803</v>
       </c>
       <c r="R27" t="n">
         <v>10.1</v>
@@ -5271,7 +5338,7 @@
         <v>6.8</v>
       </c>
       <c r="X27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="n">
         <v>5.2</v>
@@ -5280,16 +5347,16 @@
         <v>23.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-9.4</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5301,7 +5368,7 @@
         <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI27" t="n">
         <v>20</v>
@@ -5313,10 +5380,10 @@
         <v>24</v>
       </c>
       <c r="AL27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AM27" t="n">
         <v>15</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>14</v>
       </c>
       <c r="AN27" t="n">
         <v>21</v>
@@ -5325,28 +5392,28 @@
         <v>6</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ27" t="n">
         <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS27" t="n">
         <v>28</v>
       </c>
       <c r="AT27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AU27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX27" t="n">
         <v>26</v>
@@ -5361,7 +5428,7 @@
         <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5480,7 +5547,7 @@
         <v>5</v>
       </c>
       <c r="AG28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
@@ -5492,10 +5559,10 @@
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM28" t="n">
         <v>8</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
@@ -5534,7 +5601,7 @@
         <v>24</v>
       </c>
       <c r="AY28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5543,7 +5610,7 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E29" t="n">
         <v>21</v>
       </c>
       <c r="F29" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G29" t="n">
-        <v>0.368</v>
+        <v>0.375</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
@@ -5593,10 +5660,10 @@
         <v>35.9</v>
       </c>
       <c r="J29" t="n">
-        <v>78.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L29" t="n">
         <v>6</v>
@@ -5605,7 +5672,7 @@
         <v>16.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.371</v>
+        <v>0.373</v>
       </c>
       <c r="O29" t="n">
         <v>18.7</v>
@@ -5614,34 +5681,34 @@
         <v>22.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.826</v>
+        <v>0.828</v>
       </c>
       <c r="R29" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="S29" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T29" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="U29" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V29" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W29" t="n">
         <v>6.2</v>
       </c>
       <c r="X29" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y29" t="n">
         <v>4.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA29" t="n">
         <v>20.5</v>
@@ -5650,10 +5717,10 @@
         <v>96.59999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.5</v>
+        <v>-3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5668,13 +5735,13 @@
         <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ29" t="n">
         <v>23</v>
       </c>
       <c r="AK29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
         <v>21</v>
@@ -5683,13 +5750,13 @@
         <v>21</v>
       </c>
       <c r="AN29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5707,22 +5774,22 @@
         <v>11</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ29" t="n">
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>2.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>9</v>
       </c>
       <c r="AF30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH30" t="n">
         <v>16</v>
@@ -5856,7 +5923,7 @@
         <v>18</v>
       </c>
       <c r="AK30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL30" t="n">
         <v>26</v>
@@ -5874,13 +5941,13 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR30" t="n">
         <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
         <v>17</v>
@@ -5889,7 +5956,7 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
@@ -5939,97 +6006,97 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F31" t="n">
         <v>42</v>
       </c>
       <c r="G31" t="n">
-        <v>0.236</v>
+        <v>0.222</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J31" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M31" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.327</v>
+        <v>0.328</v>
       </c>
       <c r="O31" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P31" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="Q31" t="n">
         <v>0.763</v>
       </c>
       <c r="R31" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S31" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="T31" t="n">
-        <v>40</v>
+        <v>39.8</v>
       </c>
       <c r="U31" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V31" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W31" t="n">
         <v>7.4</v>
       </c>
       <c r="X31" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y31" t="n">
         <v>5.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.4</v>
+        <v>-7.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG31" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI31" t="n">
         <v>19</v>
@@ -6053,10 +6120,10 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR31" t="n">
         <v>9</v>
@@ -6068,13 +6135,13 @@
         <v>24</v>
       </c>
       <c r="AU31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV31" t="n">
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-20-2008-09</t>
+          <t>2009-02-20</t>
         </is>
       </c>
     </row>
